--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/101.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/101.xlsx
@@ -426,13 +426,13 @@
         <v>-0.8460587418865577</v>
       </c>
       <c r="E2">
-        <v>-11.34220374375309</v>
+        <v>-8.162205140664792</v>
       </c>
       <c r="F2">
-        <v>-3.860333895119083</v>
+        <v>-4.101632349350162</v>
       </c>
       <c r="G2">
-        <v>-8.121550647247824</v>
+        <v>-6.929025933091557</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-0.7592803780763675</v>
       </c>
       <c r="E3">
-        <v>-11.94662369803086</v>
+        <v>-9.140966870312624</v>
       </c>
       <c r="F3">
-        <v>-3.854326574713981</v>
+        <v>-3.882465387019677</v>
       </c>
       <c r="G3">
-        <v>-6.872273250911831</v>
+        <v>-7.214285710573937</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-0.6483457408956007</v>
       </c>
       <c r="E4">
-        <v>-13.03828934163793</v>
+        <v>-9.238528314333875</v>
       </c>
       <c r="F4">
-        <v>-3.815986417842808</v>
+        <v>-3.819975835254691</v>
       </c>
       <c r="G4">
-        <v>-7.453624910881087</v>
+        <v>-6.970788465069463</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-0.5125994161829649</v>
       </c>
       <c r="E5">
-        <v>-13.65123188399814</v>
+        <v>-10.26468052447198</v>
       </c>
       <c r="F5">
-        <v>-3.945442018817509</v>
+        <v>-4.117266955710599</v>
       </c>
       <c r="G5">
-        <v>-6.948217165582712</v>
+        <v>-6.315936073037308</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.3432761275692389</v>
       </c>
       <c r="E6">
-        <v>-13.31318582779956</v>
+        <v>-11.94598518319578</v>
       </c>
       <c r="F6">
-        <v>-3.619278980904427</v>
+        <v>-3.752448152945878</v>
       </c>
       <c r="G6">
-        <v>-6.835251420146161</v>
+        <v>-6.413756072631693</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.1369024801084585</v>
       </c>
       <c r="E7">
-        <v>-14.99516975762451</v>
+        <v>-12.06733922965333</v>
       </c>
       <c r="F7">
-        <v>-3.854966074348942</v>
+        <v>-3.743055294965534</v>
       </c>
       <c r="G7">
-        <v>-6.941536484684462</v>
+        <v>-6.424296849628733</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>0.1054733241507601</v>
       </c>
       <c r="E8">
-        <v>-17.15923238793601</v>
+        <v>-13.17474132043706</v>
       </c>
       <c r="F8">
-        <v>-4.097597371731125</v>
+        <v>-3.732383437715268</v>
       </c>
       <c r="G8">
-        <v>-6.884244183581836</v>
+        <v>-5.289868899141135</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>0.3851109684552753</v>
       </c>
       <c r="E9">
-        <v>-15.56775453962836</v>
+        <v>-14.21485934441482</v>
       </c>
       <c r="F9">
-        <v>-4.136739388248207</v>
+        <v>-3.777309943806099</v>
       </c>
       <c r="G9">
-        <v>-7.079420706395108</v>
+        <v>-6.105580698926477</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.7007881747493939</v>
       </c>
       <c r="E10">
-        <v>-16.14837283452181</v>
+        <v>-14.73647162298833</v>
       </c>
       <c r="F10">
-        <v>-3.858719407051026</v>
+        <v>-3.410262004360444</v>
       </c>
       <c r="G10">
-        <v>-6.135786116426788</v>
+        <v>-5.114390122286527</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>1.044608578259553</v>
       </c>
       <c r="E11">
-        <v>-18.36388345803446</v>
+        <v>-15.64320797354416</v>
       </c>
       <c r="F11">
-        <v>-3.869419428792988</v>
+        <v>-3.602366203641469</v>
       </c>
       <c r="G11">
-        <v>-6.383957852232713</v>
+        <v>-5.334266625368302</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.411526566952753</v>
       </c>
       <c r="E12">
-        <v>-18.71956792049292</v>
+        <v>-15.87087247580578</v>
       </c>
       <c r="F12">
-        <v>-3.767624672132567</v>
+        <v>-3.489652736244749</v>
       </c>
       <c r="G12">
-        <v>-5.073071203410883</v>
+        <v>-5.300062068856551</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>1.791691801093885</v>
       </c>
       <c r="E13">
-        <v>-20.62459278061766</v>
+        <v>-16.25896722673714</v>
       </c>
       <c r="F13">
-        <v>-3.232170468065175</v>
+        <v>-3.624681593105485</v>
       </c>
       <c r="G13">
-        <v>-4.470800206178972</v>
+        <v>-4.287624410945559</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.169267798487509</v>
       </c>
       <c r="E14">
-        <v>-20.08689536236891</v>
+        <v>-17.79476295864648</v>
       </c>
       <c r="F14">
-        <v>-3.516527459893773</v>
+        <v>-3.206729648390397</v>
       </c>
       <c r="G14">
-        <v>-4.194194194736247</v>
+        <v>-4.111317997706132</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.532345691398224</v>
       </c>
       <c r="E15">
-        <v>-21.74112880347486</v>
+        <v>-18.13568459583993</v>
       </c>
       <c r="F15">
-        <v>-3.828785522583463</v>
+        <v>-3.087445570754671</v>
       </c>
       <c r="G15">
-        <v>-4.087415858912594</v>
+        <v>-3.231663010829767</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.866346740344858</v>
       </c>
       <c r="E16">
-        <v>-21.68292432705427</v>
+        <v>-19.79282984573282</v>
       </c>
       <c r="F16">
-        <v>-3.320996304667367</v>
+        <v>-3.127308266912189</v>
       </c>
       <c r="G16">
-        <v>-3.471128011867409</v>
+        <v>-3.417871265777153</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.154842788106999</v>
       </c>
       <c r="E17">
-        <v>-22.68715872299525</v>
+        <v>-20.03992150148734</v>
       </c>
       <c r="F17">
-        <v>-3.143514446780558</v>
+        <v>-2.87988486410481</v>
       </c>
       <c r="G17">
-        <v>-3.376198118528808</v>
+        <v>-2.528367405921457</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.387393402711412</v>
       </c>
       <c r="E18">
-        <v>-24.25791880271781</v>
+        <v>-21.29088980373624</v>
       </c>
       <c r="F18">
-        <v>-3.059626508266455</v>
+        <v>-2.561641846929893</v>
       </c>
       <c r="G18">
-        <v>-2.860524371513153</v>
+        <v>-2.045799114298514</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.554681060383114</v>
       </c>
       <c r="E19">
-        <v>-24.08700060824631</v>
+        <v>-21.30246458329984</v>
       </c>
       <c r="F19">
-        <v>-2.535174680043046</v>
+        <v>-2.311484003325873</v>
       </c>
       <c r="G19">
-        <v>-3.166034756059255</v>
+        <v>-2.627283196089341</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.651594159359495</v>
       </c>
       <c r="E20">
-        <v>-24.7329376122264</v>
+        <v>-22.82118796820027</v>
       </c>
       <c r="F20">
-        <v>-2.101626233868049</v>
+        <v>-2.251246782529099</v>
       </c>
       <c r="G20">
-        <v>-1.872260317129918</v>
+        <v>-1.818275251021023</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.680414428188135</v>
       </c>
       <c r="E21">
-        <v>-25.7195924720696</v>
+        <v>-23.4060449147649</v>
       </c>
       <c r="F21">
-        <v>-2.204819274704395</v>
+        <v>-1.767228395603737</v>
       </c>
       <c r="G21">
-        <v>-1.790463357945606</v>
+        <v>-1.918852935049621</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.64503319536728</v>
       </c>
       <c r="E22">
-        <v>-26.59834738173204</v>
+        <v>-23.94613336728971</v>
       </c>
       <c r="F22">
-        <v>-1.928828793644073</v>
+        <v>-1.827453190889469</v>
       </c>
       <c r="G22">
-        <v>-2.205681911117616</v>
+        <v>-1.472664228357729</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.551472998906284</v>
       </c>
       <c r="E23">
-        <v>-25.87558028773782</v>
+        <v>-23.30621923373982</v>
       </c>
       <c r="F23">
-        <v>-2.271901295350502</v>
+        <v>-1.52098044614093</v>
       </c>
       <c r="G23">
-        <v>-1.492050783035701</v>
+        <v>-1.867069381724341</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.405294507205116</v>
       </c>
       <c r="E24">
-        <v>-26.43104743799267</v>
+        <v>-24.66402329477767</v>
       </c>
       <c r="F24">
-        <v>-1.561876944817142</v>
+        <v>-1.100978292103914</v>
       </c>
       <c r="G24">
-        <v>-2.312420520394797</v>
+        <v>-1.90950064390118</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.209994138508058</v>
       </c>
       <c r="E25">
-        <v>-26.59713375069799</v>
+        <v>-24.39308016642475</v>
       </c>
       <c r="F25">
-        <v>-1.459769893645867</v>
+        <v>-0.7027630291279271</v>
       </c>
       <c r="G25">
-        <v>-2.320286376596106</v>
+        <v>-2.419337899131099</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.972070244450123</v>
       </c>
       <c r="E26">
-        <v>-28.07578919757854</v>
+        <v>-24.44078764009556</v>
       </c>
       <c r="F26">
-        <v>-1.221256410622999</v>
+        <v>-0.7189070814410867</v>
       </c>
       <c r="G26">
-        <v>-2.270965869152044</v>
+        <v>-2.049881016948435</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.697703468279315</v>
       </c>
       <c r="E27">
-        <v>-27.24016347436516</v>
+        <v>-24.65178282953494</v>
       </c>
       <c r="F27">
-        <v>-1.238174986457776</v>
+        <v>-0.5993264482751585</v>
       </c>
       <c r="G27">
-        <v>-2.907153405433788</v>
+        <v>-2.787142819089668</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.394178496060405</v>
       </c>
       <c r="E28">
-        <v>-27.8813501091112</v>
+        <v>-24.57008010148855</v>
       </c>
       <c r="F28">
-        <v>-1.304175159275827</v>
+        <v>-0.8098485683900276</v>
       </c>
       <c r="G28">
-        <v>-2.936325932725845</v>
+        <v>-2.964644339268771</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.074130874843161</v>
       </c>
       <c r="E29">
-        <v>-26.98562247886801</v>
+        <v>-25.07722843408157</v>
       </c>
       <c r="F29">
-        <v>-1.126984058347402</v>
+        <v>-0.6852024685559804</v>
       </c>
       <c r="G29">
-        <v>-2.332025571078361</v>
+        <v>-3.149736940369423</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.748981462993731</v>
       </c>
       <c r="E30">
-        <v>-27.60797519021616</v>
+        <v>-24.03593753533582</v>
       </c>
       <c r="F30">
-        <v>-1.127740357786158</v>
+        <v>-0.7016596437473982</v>
       </c>
       <c r="G30">
-        <v>-3.807588686660158</v>
+        <v>-2.370772196069991</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.430452753143963</v>
       </c>
       <c r="E31">
-        <v>-27.06949434596408</v>
+        <v>-24.36931020635849</v>
       </c>
       <c r="F31">
-        <v>-1.425774523802378</v>
+        <v>-0.5206042088849131</v>
       </c>
       <c r="G31">
-        <v>-3.147091814483546</v>
+        <v>-3.362727508729513</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.132824799912816</v>
       </c>
       <c r="E32">
-        <v>-26.0420017075197</v>
+        <v>-23.9201535119077</v>
       </c>
       <c r="F32">
-        <v>-1.311220424036637</v>
+        <v>-0.6074593594358441</v>
       </c>
       <c r="G32">
-        <v>-2.624538753837285</v>
+        <v>-3.325262064861581</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.866427271693017</v>
       </c>
       <c r="E33">
-        <v>-26.05406103380213</v>
+        <v>-23.87940177431268</v>
       </c>
       <c r="F33">
-        <v>-1.078956973067892</v>
+        <v>-0.4322729076221933</v>
       </c>
       <c r="G33">
-        <v>-3.270899596561209</v>
+        <v>-3.157529964568867</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.6404135849651192</v>
       </c>
       <c r="E34">
-        <v>-26.4033739333318</v>
+        <v>-22.92757993653647</v>
       </c>
       <c r="F34">
-        <v>-1.286807608308733</v>
+        <v>-0.6071338110465438</v>
       </c>
       <c r="G34">
-        <v>-3.455022207818855</v>
+        <v>-3.431573613764197</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.4646863606081491</v>
       </c>
       <c r="E35">
-        <v>-25.09079574220855</v>
+        <v>-22.91754936660949</v>
       </c>
       <c r="F35">
-        <v>-1.05231087882204</v>
+        <v>-0.7319257035434837</v>
       </c>
       <c r="G35">
-        <v>-4.558172124051418</v>
+        <v>-3.562800328395368</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.3444235783447889</v>
       </c>
       <c r="E36">
-        <v>-24.70679473178012</v>
+        <v>-22.62717908476365</v>
       </c>
       <c r="F36">
-        <v>-1.425808486865892</v>
+        <v>-0.7359499123862837</v>
       </c>
       <c r="G36">
-        <v>-3.59599516851764</v>
+        <v>-4.261239362997567</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.281798457507258</v>
       </c>
       <c r="E37">
-        <v>-24.63568410443767</v>
+        <v>-21.41549982300531</v>
       </c>
       <c r="F37">
-        <v>-1.28509951472416</v>
+        <v>-0.8874193770903818</v>
       </c>
       <c r="G37">
-        <v>-4.148316654653027</v>
+        <v>-4.115101951257519</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.2770649435413024</v>
       </c>
       <c r="E38">
-        <v>-23.19595994860106</v>
+        <v>-21.34707910922342</v>
       </c>
       <c r="F38">
-        <v>-1.338363538724168</v>
+        <v>-0.438918070927451</v>
       </c>
       <c r="G38">
-        <v>-4.129615382901684</v>
+        <v>-4.407674723836149</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.3251836220837337</v>
       </c>
       <c r="E39">
-        <v>-22.98688936061493</v>
+        <v>-21.02164485313619</v>
       </c>
       <c r="F39">
-        <v>-1.296071240974239</v>
+        <v>-0.8016087978343809</v>
       </c>
       <c r="G39">
-        <v>-4.253267569339002</v>
+        <v>-4.141857780305909</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.4173907836428551</v>
       </c>
       <c r="E40">
-        <v>-23.23599165882887</v>
+        <v>-20.04215856764713</v>
       </c>
       <c r="F40">
-        <v>-1.245669226350903</v>
+        <v>-0.8998092683340539</v>
       </c>
       <c r="G40">
-        <v>-4.064761795787361</v>
+        <v>-4.534157426709545</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.5436121077193199</v>
       </c>
       <c r="E41">
-        <v>-20.36373909235382</v>
+        <v>-19.68435025087907</v>
       </c>
       <c r="F41">
-        <v>-1.251838906766954</v>
+        <v>-0.7006465504137744</v>
       </c>
       <c r="G41">
-        <v>-4.930201300118096</v>
+        <v>-3.918763426959963</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.6925514721229348</v>
       </c>
       <c r="E42">
-        <v>-21.43777991512304</v>
+        <v>-18.73870978012334</v>
       </c>
       <c r="F42">
-        <v>-1.546192636412536</v>
+        <v>-0.9772541651891825</v>
       </c>
       <c r="G42">
-        <v>-4.152924934043693</v>
+        <v>-3.749333016805603</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.8528243410241889</v>
       </c>
       <c r="E43">
-        <v>-21.5917253890138</v>
+        <v>-17.76635584119636</v>
       </c>
       <c r="F43">
-        <v>-1.972086139418263</v>
+        <v>-0.9544210460984169</v>
       </c>
       <c r="G43">
-        <v>-4.47112795018736</v>
+        <v>-3.992144979383448</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.014859256711731</v>
       </c>
       <c r="E44">
-        <v>-20.08583569945111</v>
+        <v>-16.98296606566145</v>
       </c>
       <c r="F44">
-        <v>-1.694197868638127</v>
+        <v>-0.9451159950627701</v>
       </c>
       <c r="G44">
-        <v>-3.855882924987046</v>
+        <v>-4.141708805756641</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.170567572323103</v>
       </c>
       <c r="E45">
-        <v>-19.1186578063149</v>
+        <v>-15.92261934829143</v>
       </c>
       <c r="F45">
-        <v>-1.42333415343373</v>
+        <v>-1.062803808713301</v>
       </c>
       <c r="G45">
-        <v>-3.315194695876658</v>
+        <v>-3.87521651093639</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.312103693872904</v>
       </c>
       <c r="E46">
-        <v>-18.28111653859627</v>
+        <v>-15.4601489402581</v>
       </c>
       <c r="F46">
-        <v>-1.449623221328975</v>
+        <v>-0.9907963154901488</v>
       </c>
       <c r="G46">
-        <v>-3.289190360665683</v>
+        <v>-3.727787986436026</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.433248784569497</v>
       </c>
       <c r="E47">
-        <v>-17.85910351734746</v>
+        <v>-14.92256473385953</v>
       </c>
       <c r="F47">
-        <v>-1.65723528675781</v>
+        <v>-1.201267905193447</v>
       </c>
       <c r="G47">
-        <v>-3.742731789000296</v>
+        <v>-3.947277155689705</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.529801124792397</v>
       </c>
       <c r="E48">
-        <v>-17.476850497886</v>
+        <v>-14.44292235238911</v>
       </c>
       <c r="F48">
-        <v>-0.8195222429199203</v>
+        <v>-1.299669668972</v>
       </c>
       <c r="G48">
-        <v>-4.339007388260587</v>
+        <v>-3.705484841137956</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.598399500048225</v>
       </c>
       <c r="E49">
-        <v>-16.72828015899606</v>
+        <v>-13.20446622382341</v>
       </c>
       <c r="F49">
-        <v>-1.252194276382755</v>
+        <v>-1.209164731644335</v>
       </c>
       <c r="G49">
-        <v>-4.055694211555298</v>
+        <v>-3.71845555856082</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.637648885425353</v>
       </c>
       <c r="E50">
-        <v>-14.61936981362398</v>
+        <v>-12.85813306019078</v>
       </c>
       <c r="F50">
-        <v>-1.51191976348911</v>
+        <v>-1.144559529532599</v>
       </c>
       <c r="G50">
-        <v>-4.797339175990525</v>
+        <v>-4.646381609945299</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.647187101728462</v>
       </c>
       <c r="E51">
-        <v>-15.8388878638896</v>
+        <v>-11.99181334015341</v>
       </c>
       <c r="F51">
-        <v>-1.506823647227087</v>
+        <v>-1.357180732646162</v>
       </c>
       <c r="G51">
-        <v>-4.466794446076454</v>
+        <v>-4.13067475747425</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.626932801098661</v>
       </c>
       <c r="E52">
-        <v>-13.99136556671426</v>
+        <v>-11.78099023272631</v>
       </c>
       <c r="F52">
-        <v>-1.143085035555615</v>
+        <v>-0.921722899607712</v>
       </c>
       <c r="G52">
-        <v>-3.534422332032735</v>
+        <v>-4.371510324365151</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.577645732702487</v>
       </c>
       <c r="E53">
-        <v>-13.51983821066558</v>
+        <v>-10.90425049399729</v>
       </c>
       <c r="F53">
-        <v>-1.030655698178055</v>
+        <v>-1.150253727059442</v>
       </c>
       <c r="G53">
-        <v>-4.405287820502335</v>
+        <v>-3.828117379549179</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.499545804894037</v>
       </c>
       <c r="E54">
-        <v>-13.8796888692111</v>
+        <v>-10.48894414275384</v>
       </c>
       <c r="F54">
-        <v>-1.423609999778862</v>
+        <v>-1.360242378566909</v>
       </c>
       <c r="G54">
-        <v>-4.975860344195724</v>
+        <v>-4.318333031367838</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.393486772317932</v>
       </c>
       <c r="E55">
-        <v>-12.82947687667025</v>
+        <v>-10.25263478361157</v>
       </c>
       <c r="F55">
-        <v>-1.830396380271616</v>
+        <v>-1.57572724779195</v>
       </c>
       <c r="G55">
-        <v>-4.512907034892963</v>
+        <v>-4.978028751523946</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.260727828558749</v>
       </c>
       <c r="E56">
-        <v>-11.66705835516733</v>
+        <v>-8.653250219686527</v>
       </c>
       <c r="F56">
-        <v>-1.145492271228151</v>
+        <v>-1.485153555969852</v>
       </c>
       <c r="G56">
-        <v>-5.761313757752127</v>
+        <v>-5.116730677982791</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.101307915866997</v>
       </c>
       <c r="E57">
-        <v>-12.91673604232405</v>
+        <v>-8.384526043597361</v>
       </c>
       <c r="F57">
-        <v>-1.456436543217001</v>
+        <v>-1.503695731914116</v>
       </c>
       <c r="G57">
-        <v>-6.164716973894478</v>
+        <v>-5.423353405830089</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.9174350636194962</v>
       </c>
       <c r="E58">
-        <v>-11.28704240186566</v>
+        <v>-8.334228282794166</v>
       </c>
       <c r="F58">
-        <v>-1.393575054488158</v>
+        <v>-1.439908128428943</v>
       </c>
       <c r="G58">
-        <v>-5.393243994150417</v>
+        <v>-5.178684227204712</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.712500113646554</v>
       </c>
       <c r="E59">
-        <v>-10.0212207048716</v>
+        <v>-6.960148886172742</v>
       </c>
       <c r="F59">
-        <v>-1.173169682890488</v>
+        <v>-1.689427300765404</v>
       </c>
       <c r="G59">
-        <v>-5.999557167485778</v>
+        <v>-4.930303927029813</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.4895776471748818</v>
       </c>
       <c r="E60">
-        <v>-12.05260810370638</v>
+        <v>-7.198373789820248</v>
       </c>
       <c r="F60">
-        <v>-1.548743179645756</v>
+        <v>-1.457665840442756</v>
       </c>
       <c r="G60">
-        <v>-5.965918714261243</v>
+        <v>-5.371129549948086</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.2551641803336643</v>
       </c>
       <c r="E61">
-        <v>-10.09746209326474</v>
+        <v>-6.554479127617616</v>
       </c>
       <c r="F61">
-        <v>-1.993695759855094</v>
+        <v>-1.767153842537485</v>
       </c>
       <c r="G61">
-        <v>-6.25374416453656</v>
+        <v>-5.818847728679121</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.01627315899434993</v>
       </c>
       <c r="E62">
-        <v>-8.64175695265506</v>
+        <v>-5.833659277446687</v>
       </c>
       <c r="F62">
-        <v>-1.601549116472016</v>
+        <v>-1.806599041523992</v>
       </c>
       <c r="G62">
-        <v>-6.288385713059493</v>
+        <v>-6.121441522605125</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.2212055831891155</v>
       </c>
       <c r="E63">
-        <v>-10.931240199083</v>
+        <v>-5.85979762941896</v>
       </c>
       <c r="F63">
-        <v>-1.768654015903955</v>
+        <v>-1.828547464228567</v>
       </c>
       <c r="G63">
-        <v>-5.95657635474942</v>
+        <v>-6.141774893307329</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.4484035210386019</v>
       </c>
       <c r="E64">
-        <v>-9.769229240240779</v>
+        <v>-5.3755271475127</v>
       </c>
       <c r="F64">
-        <v>-2.194758752597395</v>
+        <v>-1.704240995029668</v>
       </c>
       <c r="G64">
-        <v>-6.297999537305537</v>
+        <v>-6.697267882069338</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.6566499687614292</v>
       </c>
       <c r="E65">
-        <v>-8.686348836208591</v>
+        <v>-5.479179389074266</v>
       </c>
       <c r="F65">
-        <v>-2.226276475539111</v>
+        <v>-1.87845742861464</v>
       </c>
       <c r="G65">
-        <v>-6.930853354229234</v>
+        <v>-6.098340535832091</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.8390657132418147</v>
       </c>
       <c r="E66">
-        <v>-9.666958183251552</v>
+        <v>-5.934259327527084</v>
       </c>
       <c r="F66">
-        <v>-1.853933611654761</v>
+        <v>-1.977209591804578</v>
       </c>
       <c r="G66">
-        <v>-5.989509661774091</v>
+        <v>-6.55190513798548</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.9879400308679964</v>
       </c>
       <c r="E67">
-        <v>-8.921150213506298</v>
+        <v>-5.027640717295448</v>
       </c>
       <c r="F67">
-        <v>-2.012546088473199</v>
+        <v>-2.200471174207101</v>
       </c>
       <c r="G67">
-        <v>-7.260500926302162</v>
+        <v>-6.96289943504938</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.097623953009441</v>
       </c>
       <c r="E68">
-        <v>-8.871930229516929</v>
+        <v>-4.840646440096715</v>
       </c>
       <c r="F68">
-        <v>-2.313197067114863</v>
+        <v>-2.005668982295158</v>
       </c>
       <c r="G68">
-        <v>-7.536818920282972</v>
+        <v>-6.88649535454854</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.164948798436518</v>
       </c>
       <c r="E69">
-        <v>-9.080914776496908</v>
+        <v>-6.250496252904728</v>
       </c>
       <c r="F69">
-        <v>-1.71445310837138</v>
+        <v>-1.937613629950761</v>
       </c>
       <c r="G69">
-        <v>-5.689448435185628</v>
+        <v>-7.124910912650233</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.187796127126687</v>
       </c>
       <c r="E70">
-        <v>-8.058946876341892</v>
+        <v>-4.826526658140799</v>
       </c>
       <c r="F70">
-        <v>-1.695773423438251</v>
+        <v>-2.212403806644427</v>
       </c>
       <c r="G70">
-        <v>-7.696294520000744</v>
+        <v>-6.469313647871742</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.166306766479773</v>
       </c>
       <c r="E71">
-        <v>-9.141138952324917</v>
+        <v>-5.34183982936964</v>
       </c>
       <c r="F71">
-        <v>-2.476698568344624</v>
+        <v>-2.251203707424153</v>
       </c>
       <c r="G71">
-        <v>-6.951835591857135</v>
+        <v>-5.882592283037788</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.102568375433548</v>
       </c>
       <c r="E72">
-        <v>-8.895337911662578</v>
+        <v>-5.563798454381595</v>
       </c>
       <c r="F72">
-        <v>-2.190088417180411</v>
+        <v>-2.552956414711541</v>
       </c>
       <c r="G72">
-        <v>-6.116962354490492</v>
+        <v>-5.827974902730892</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.000845359291274</v>
       </c>
       <c r="E73">
-        <v>-8.843518583592806</v>
+        <v>-4.850763051029851</v>
       </c>
       <c r="F73">
-        <v>-2.504957493923726</v>
+        <v>-2.667536193866768</v>
       </c>
       <c r="G73">
-        <v>-5.207005944293178</v>
+        <v>-5.857998240226542</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.8665014568567513</v>
       </c>
       <c r="E74">
-        <v>-8.569908184049362</v>
+        <v>-5.50364673413771</v>
       </c>
       <c r="F74">
-        <v>-2.56620946478893</v>
+        <v>-2.783082677781063</v>
       </c>
       <c r="G74">
-        <v>-6.618255091683553</v>
+        <v>-5.577436126864388</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.7051391471780646</v>
       </c>
       <c r="E75">
-        <v>-9.189032093430038</v>
+        <v>-5.744149460211075</v>
       </c>
       <c r="F75">
-        <v>-2.42525860936558</v>
+        <v>-2.621284299931458</v>
       </c>
       <c r="G75">
-        <v>-5.852181611714043</v>
+        <v>-6.058051196619161</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.5242467337140637</v>
       </c>
       <c r="E76">
-        <v>-11.14408300591752</v>
+        <v>-5.706916346920009</v>
       </c>
       <c r="F76">
-        <v>-2.511472603546744</v>
+        <v>-2.693949516872433</v>
       </c>
       <c r="G76">
-        <v>-5.810839519019624</v>
+        <v>-5.671035180896202</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.3289097825089827</v>
       </c>
       <c r="E77">
-        <v>-10.78262926757328</v>
+        <v>-6.369961925701079</v>
       </c>
       <c r="F77">
-        <v>-3.060531913837715</v>
+        <v>-2.722273883476356</v>
       </c>
       <c r="G77">
-        <v>-4.754441126892649</v>
+        <v>-5.038356822886086</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.1214034026324631</v>
       </c>
       <c r="E78">
-        <v>-10.52179369320548</v>
+        <v>-7.607317635082921</v>
       </c>
       <c r="F78">
-        <v>-2.653184728613267</v>
+        <v>-2.74868389301241</v>
       </c>
       <c r="G78">
-        <v>-5.524530298601295</v>
+        <v>-4.675365436141617</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.09476456982584743</v>
       </c>
       <c r="E79">
-        <v>-12.31162775999711</v>
+        <v>-7.461075095479214</v>
       </c>
       <c r="F79">
-        <v>-2.945692027318008</v>
+        <v>-2.910668653527646</v>
       </c>
       <c r="G79">
-        <v>-4.607767406775239</v>
+        <v>-4.248887717590546</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.3206872093547725</v>
       </c>
       <c r="E80">
-        <v>-11.07537699827314</v>
+        <v>-9.82412340216176</v>
       </c>
       <c r="F80">
-        <v>-3.109384881417816</v>
+        <v>-3.273163057360112</v>
       </c>
       <c r="G80">
-        <v>-4.271363011256659</v>
+        <v>-4.498963017081552</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.5594405200680803</v>
       </c>
       <c r="E81">
-        <v>-12.08499574980924</v>
+        <v>-9.726955935379177</v>
       </c>
       <c r="F81">
-        <v>-2.963260871563983</v>
+        <v>-2.982532839190114</v>
       </c>
       <c r="G81">
-        <v>-4.326106192294047</v>
+        <v>-4.238744206058219</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.8096648386807375</v>
       </c>
       <c r="E82">
-        <v>-14.61727313015843</v>
+        <v>-9.697507268907296</v>
       </c>
       <c r="F82">
-        <v>-3.178473207913503</v>
+        <v>-3.106319922027458</v>
       </c>
       <c r="G82">
-        <v>-4.039790350784639</v>
+        <v>-3.497817630005013</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.072621081655568</v>
       </c>
       <c r="E83">
-        <v>-14.71800903445905</v>
+        <v>-11.22509287744073</v>
       </c>
       <c r="F83">
-        <v>-3.0993492103329</v>
+        <v>-3.433106720594849</v>
       </c>
       <c r="G83">
-        <v>-3.492778979694243</v>
+        <v>-3.594853030306591</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.347955784256773</v>
       </c>
       <c r="E84">
-        <v>-15.70290684638728</v>
+        <v>-12.49023077485963</v>
       </c>
       <c r="F84">
-        <v>-3.326138809503946</v>
+        <v>-3.542003070999469</v>
       </c>
       <c r="G84">
-        <v>-3.902449058542434</v>
+        <v>-3.65736275117911</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.628440353409877</v>
       </c>
       <c r="E85">
-        <v>-16.43768798192386</v>
+        <v>-13.1507358797224</v>
       </c>
       <c r="F85">
-        <v>-3.105107192149759</v>
+        <v>-3.427561629200509</v>
       </c>
       <c r="G85">
-        <v>-3.216176278797056</v>
+        <v>-2.638168269822464</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.908303580159939</v>
       </c>
       <c r="E86">
-        <v>-16.80507854969214</v>
+        <v>-15.10430598120937</v>
       </c>
       <c r="F86">
-        <v>-3.445528089799827</v>
+        <v>-3.494725658219493</v>
       </c>
       <c r="G86">
-        <v>-3.807409917201037</v>
+        <v>-2.29328556717781</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.179313743065955</v>
       </c>
       <c r="E87">
-        <v>-19.02627240808442</v>
+        <v>-16.33495954905985</v>
       </c>
       <c r="F87">
-        <v>-3.652137002303872</v>
+        <v>-3.543812225407183</v>
       </c>
       <c r="G87">
-        <v>-2.880337986565691</v>
+        <v>-2.426842905868627</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.428731038286383</v>
       </c>
       <c r="E88">
-        <v>-19.78501369959558</v>
+        <v>-17.70214660824161</v>
       </c>
       <c r="F88">
-        <v>-3.795493436664951</v>
+        <v>-3.720008457084846</v>
       </c>
       <c r="G88">
-        <v>-3.010121303341739</v>
+        <v>-2.195220587213519</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.647379301217695</v>
       </c>
       <c r="E89">
-        <v>-21.14311211144393</v>
+        <v>-18.93337529229107</v>
       </c>
       <c r="F89">
-        <v>-3.574395549918541</v>
+        <v>-3.798385267268124</v>
       </c>
       <c r="G89">
-        <v>-2.669780669176965</v>
+        <v>-2.346684666726254</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.825741560848477</v>
       </c>
       <c r="E90">
-        <v>-22.64549676212468</v>
+        <v>-21.75191562856113</v>
       </c>
       <c r="F90">
-        <v>-3.65146188287059</v>
+        <v>-3.876134174960081</v>
       </c>
       <c r="G90">
-        <v>-2.773976779479986</v>
+        <v>-1.920693598369456</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.953603561152319</v>
       </c>
       <c r="E91">
-        <v>-24.56560596916897</v>
+        <v>-22.66342951919506</v>
       </c>
       <c r="F91">
-        <v>-3.669401007345616</v>
+        <v>-3.833194922268565</v>
       </c>
       <c r="G91">
-        <v>-2.689816090780634</v>
+        <v>-1.976115441242394</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.026059988395305</v>
       </c>
       <c r="E92">
-        <v>-26.24837332499726</v>
+        <v>-24.30594326956916</v>
       </c>
       <c r="F92">
-        <v>-3.635271441982874</v>
+        <v>-3.991997095222244</v>
       </c>
       <c r="G92">
-        <v>-1.813686834903593</v>
+        <v>-2.431295589618947</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.040104536452888</v>
       </c>
       <c r="E93">
-        <v>-28.67440817665249</v>
+        <v>-26.63323927396114</v>
       </c>
       <c r="F93">
-        <v>-4.233274840268254</v>
+        <v>-4.336129907204257</v>
       </c>
       <c r="G93">
-        <v>-2.677666388651509</v>
+        <v>-2.212154027646891</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.995673615767438</v>
       </c>
       <c r="E94">
-        <v>-30.79674091898331</v>
+        <v>-28.00889910801125</v>
       </c>
       <c r="F94">
-        <v>-4.297413671532214</v>
+        <v>-4.097614767446585</v>
       </c>
       <c r="G94">
-        <v>-3.546105247240823</v>
+        <v>-3.200484292940911</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.899122843843874</v>
       </c>
       <c r="E95">
-        <v>-32.12616050494109</v>
+        <v>-31.20832486459245</v>
       </c>
       <c r="F95">
-        <v>-4.154859096817044</v>
+        <v>-4.201854036312666</v>
       </c>
       <c r="G95">
-        <v>-3.578055322240329</v>
+        <v>-1.919683881979978</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.757842424520635</v>
       </c>
       <c r="E96">
-        <v>-33.48736771419571</v>
+        <v>-32.66618103035578</v>
       </c>
       <c r="F96">
-        <v>-4.193883485162929</v>
+        <v>-4.413162277092791</v>
       </c>
       <c r="G96">
-        <v>-3.625091553262294</v>
+        <v>-3.21039275573995</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.584249435080719</v>
       </c>
       <c r="E97">
-        <v>-37.20947220497924</v>
+        <v>-34.91166335908819</v>
       </c>
       <c r="F97">
-        <v>-4.783437535939754</v>
+        <v>-4.60024905501506</v>
       </c>
       <c r="G97">
-        <v>-3.471995374798698</v>
+        <v>-3.593465911725636</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.391679608948927</v>
       </c>
       <c r="E98">
-        <v>-39.16982143205568</v>
+        <v>-37.20869104321291</v>
       </c>
       <c r="F98">
-        <v>-4.56246887450818</v>
+        <v>-4.555447632402052</v>
       </c>
       <c r="G98">
-        <v>-5.142337747729054</v>
+        <v>-3.984699562465627</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.197541928416172</v>
       </c>
       <c r="E99">
-        <v>-41.58910432896548</v>
+        <v>-39.41515603989524</v>
       </c>
       <c r="F99">
-        <v>-4.789046411624109</v>
+        <v>-4.77936196831798</v>
       </c>
       <c r="G99">
-        <v>-4.705166967086137</v>
+        <v>-4.393873059482928</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>2.013207904764436</v>
       </c>
       <c r="E100">
-        <v>-43.87129446800407</v>
+        <v>-41.68665218756471</v>
       </c>
       <c r="F100">
-        <v>-4.864200044243094</v>
+        <v>-4.890197526812554</v>
       </c>
       <c r="G100">
-        <v>-5.440343125537629</v>
+        <v>-5.397392107711124</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.861800355339654</v>
       </c>
       <c r="E101">
-        <v>-44.79437634549059</v>
+        <v>-43.64432961497663</v>
       </c>
       <c r="F101">
-        <v>-4.705505559051779</v>
+        <v>-4.63939024316474</v>
       </c>
       <c r="G101">
-        <v>-5.557390773624101</v>
+        <v>-5.051910196323862</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.741089207377068</v>
       </c>
       <c r="E102">
-        <v>-47.54579790425597</v>
+        <v>-46.2207550884266</v>
       </c>
       <c r="F102">
-        <v>-5.003186012187004</v>
+        <v>-4.591891656288215</v>
       </c>
       <c r="G102">
-        <v>-5.838525611364549</v>
+        <v>-5.311897269159446</v>
       </c>
     </row>
   </sheetData>
